--- a/TSC- CGD-Candidate Information for Certificate prepare.xlsx
+++ b/TSC- CGD-Candidate Information for Certificate prepare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BDFCF3-7540-47EA-A1D3-4049541B6A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9E00B5-A494-4F06-9B8B-1ABAFEB8DF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="210">
   <si>
     <t xml:space="preserve">Candidate ID </t>
   </si>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>11,12,13</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1287,7 @@
         <v>203</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>87</v>
